--- a/upload/contabancaria.xlsx
+++ b/upload/contabancaria.xlsx
@@ -9,27 +9,22 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19365" windowHeight="6420"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8430"/>
   </bookViews>
   <sheets>
-    <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
+    <sheet name="contabacaria" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913" refMode="R1C1"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="24">
   <si>
     <t>Ano de Exercício</t>
   </si>
   <si>
-    <t>Mês - Numérico</t>
+    <t>Mês - Descritivo</t>
   </si>
   <si>
     <t>Unidade Orçamentária - Código</t>
@@ -38,28 +33,64 @@
     <t>Unidade Orçamentária - Nome</t>
   </si>
   <si>
+    <t>Classificação Receita - Formatado</t>
+  </si>
+  <si>
     <t>Classificação Receita - Descrição</t>
   </si>
   <si>
-    <t>Classificação Receita - Formatado</t>
+    <t>Dezembro</t>
+  </si>
+  <si>
+    <t>EMG - ADMINISTRACAO DIRETA</t>
+  </si>
+  <si>
+    <t>1321.01.0.1.01.000</t>
+  </si>
+  <si>
+    <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+  </si>
+  <si>
+    <t>2999.99.0.1.04.000</t>
+  </si>
+  <si>
+    <t>DEMAIS REC. CAPITAL - PRINC. - ROMPIMENTO DA BARRAGEM DE FUNDAO EM MARIANA - ACORDO JUDICIAL DE REPARACAO INTEGRAL E DEFINITIVA</t>
+  </si>
+  <si>
+    <t>Abril</t>
+  </si>
+  <si>
+    <t>Agosto</t>
+  </si>
+  <si>
+    <t>Fevereiro</t>
+  </si>
+  <si>
+    <t>Janeiro</t>
+  </si>
+  <si>
+    <t>Julho</t>
+  </si>
+  <si>
+    <t>Junho</t>
+  </si>
+  <si>
+    <t>Maio</t>
+  </si>
+  <si>
+    <t>Março</t>
+  </si>
+  <si>
+    <t>Novembro</t>
+  </si>
+  <si>
+    <t>Outubro</t>
+  </si>
+  <si>
+    <t>Setembro</t>
   </si>
   <si>
     <t>Valor Arrecadado Líquido</t>
-  </si>
-  <si>
-    <t>EMG - ADMINISTRACAO DIRETA</t>
-  </si>
-  <si>
-    <t>DEMAIS REC. CAPITAL - PRINC. - ROMPIMENTO DA BARRAGEM DE FUNDAO EM MARIANA - ACORDO JUDICIAL DE REPARACAO INTEGRAL E DEFINITIVA</t>
-  </si>
-  <si>
-    <t>2999.99.0.1.04.000</t>
-  </si>
-  <si>
-    <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
-  </si>
-  <si>
-    <t>1321.01.0.1.01.000</t>
   </si>
 </sst>
 </file>
@@ -71,11 +102,9 @@
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="9"/>
@@ -92,13 +121,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF7F7F7"/>
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFF7F7F7"/>
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
@@ -132,19 +161,19 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -428,42 +457,44 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="4" width="10.7109375" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" customWidth="1"/>
+    <col min="3" max="4" width="10.7109375" customWidth="1"/>
     <col min="5" max="7" width="44.5703125" customWidth="1"/>
     <col min="8" max="8" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="G1" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
         <v>2024</v>
       </c>
-      <c r="B2" s="3">
-        <v>12</v>
+      <c r="B2" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C2" s="3">
         <v>9999</v>
@@ -472,21 +503,21 @@
         <v>7</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2" s="5">
         <v>310515903.98000002</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>2024</v>
       </c>
-      <c r="B3" s="3">
-        <v>12</v>
+      <c r="B3" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C3" s="3">
         <v>9999</v>
@@ -495,21 +526,21 @@
         <v>7</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G3" s="5">
         <v>310515903.98000002</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>2025</v>
       </c>
-      <c r="B4" s="3">
-        <v>1</v>
+      <c r="B4" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="C4" s="3">
         <v>9999</v>
@@ -518,19 +549,21 @@
         <v>7</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" s="5"/>
-    </row>
-    <row r="5" spans="1:7" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+        <v>8</v>
+      </c>
+      <c r="G4" s="5">
+        <v>2995148.47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>2025</v>
       </c>
-      <c r="B5" s="3">
-        <v>1</v>
+      <c r="B5" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="C5" s="3">
         <v>9999</v>
@@ -539,157 +572,155 @@
         <v>7</v>
       </c>
       <c r="E5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="5">
+        <v>14845558.060000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="3">
+        <v>9999</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6" s="5">
+        <v>27910418.219999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="3">
+        <v>9999</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G7" s="5">
+        <v>3083631.22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="3">
+        <v>9999</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="G8" s="5"/>
+    </row>
+    <row r="9" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="3">
+        <v>9999</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="5"/>
+    </row>
+    <row r="10" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="3">
+        <v>9999</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="5">
+        <v>10803651.24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="3">
+        <v>9999</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="5"/>
-    </row>
-    <row r="6" spans="1:7" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A6" s="3">
-        <v>2025</v>
-      </c>
-      <c r="B6" s="3">
-        <v>2</v>
-      </c>
-      <c r="C6" s="3">
-        <v>9999</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="4" t="s">
+      <c r="F11" s="4" t="s">
         <v>10</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" s="5">
-        <v>3083631.22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A7" s="3">
-        <v>2025</v>
-      </c>
-      <c r="B7" s="3">
-        <v>3</v>
-      </c>
-      <c r="C7" s="3">
-        <v>9999</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" s="5">
-        <v>3043139.48</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A8" s="3">
-        <v>2025</v>
-      </c>
-      <c r="B8" s="3">
-        <v>4</v>
-      </c>
-      <c r="C8" s="3">
-        <v>9999</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8" s="5">
-        <v>2995148.47</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A9" s="3">
-        <v>2025</v>
-      </c>
-      <c r="B9" s="3">
-        <v>5</v>
-      </c>
-      <c r="C9" s="3">
-        <v>9999</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9" s="5">
-        <v>3326424.56</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A10" s="3">
-        <v>2025</v>
-      </c>
-      <c r="B10" s="3">
-        <v>6</v>
-      </c>
-      <c r="C10" s="3">
-        <v>9999</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10" s="5">
-        <v>846091078.27999997</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A11" s="3">
-        <v>2025</v>
-      </c>
-      <c r="B11" s="3">
-        <v>6</v>
-      </c>
-      <c r="C11" s="3">
-        <v>9999</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>11</v>
       </c>
       <c r="G11" s="5">
         <v>846091078.27999997</v>
       </c>
     </row>
-    <row r="12" spans="1:7" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>2025</v>
       </c>
-      <c r="B12" s="3">
-        <v>7</v>
+      <c r="B12" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="C12" s="3">
         <v>9999</v>
@@ -698,21 +729,21 @@
         <v>7</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G12" s="5">
-        <v>10803651.24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+        <v>846091078.27999997</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>2025</v>
       </c>
-      <c r="B13" s="3">
-        <v>8</v>
+      <c r="B13" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="C13" s="3">
         <v>9999</v>
@@ -721,21 +752,21 @@
         <v>7</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G13" s="5">
-        <v>14845558.060000001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+        <v>3326424.56</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>2025</v>
       </c>
-      <c r="B14" s="3">
-        <v>9</v>
+      <c r="B14" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="C14" s="3">
         <v>9999</v>
@@ -744,90 +775,90 @@
         <v>7</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G14" s="5">
+        <v>3043139.48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="3">
+        <v>9999</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" s="5">
+        <v>15387953.630000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="3">
+        <v>9999</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G16" s="5">
+        <v>14539798.82</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="3">
+        <v>9999</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="5">
         <v>13717383.76</v>
       </c>
     </row>
-    <row r="15" spans="1:7" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A15" s="3">
-        <v>2025</v>
-      </c>
-      <c r="B15" s="3">
-        <v>10</v>
-      </c>
-      <c r="C15" s="3">
-        <v>9999</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G15" s="5">
-        <v>14539798.82</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A16" s="3">
-        <v>2025</v>
-      </c>
-      <c r="B16" s="3">
-        <v>11</v>
-      </c>
-      <c r="C16" s="3">
-        <v>9999</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G16" s="5">
-        <v>15387953.630000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A17" s="3">
-        <v>2025</v>
-      </c>
-      <c r="B17" s="3">
-        <v>12</v>
-      </c>
-      <c r="C17" s="3">
-        <v>9999</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G17" s="5">
-        <v>27910418.219999999</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>2026</v>
       </c>
-      <c r="B18" s="3">
-        <v>1</v>
+      <c r="B18" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="C18" s="3">
         <v>9999</v>
@@ -836,19 +867,21 @@
         <v>7</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G18" s="5"/>
-    </row>
-    <row r="19" spans="1:7" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="G18" s="5">
+        <v>494575886.38999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>2026</v>
       </c>
-      <c r="B19" s="3">
-        <v>1</v>
+      <c r="B19" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="C19" s="3">
         <v>9999</v>
@@ -857,19 +890,21 @@
         <v>7</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G19" s="5"/>
-    </row>
-    <row r="20" spans="1:7" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+        <v>8</v>
+      </c>
+      <c r="G19" s="5">
+        <v>494575886.38999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>2026</v>
       </c>
-      <c r="B20" s="3">
-        <v>2</v>
+      <c r="B20" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="C20" s="3">
         <v>9999</v>
@@ -878,21 +913,21 @@
         <v>7</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G20" s="5">
         <v>14517354.300000001</v>
       </c>
     </row>
-    <row r="21" spans="1:7" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>2026</v>
       </c>
-      <c r="B21" s="3">
-        <v>3</v>
+      <c r="B21" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="C21" s="3">
         <v>9999</v>
@@ -901,21 +936,19 @@
         <v>7</v>
       </c>
       <c r="E21" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F21" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G21" s="5">
-        <v>12551122.09</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="G21" s="5"/>
+    </row>
+    <row r="22" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>2026</v>
       </c>
-      <c r="B22" s="3">
-        <v>4</v>
+      <c r="B22" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="C22" s="3">
         <v>9999</v>
@@ -924,21 +957,19 @@
         <v>7</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G22" s="5">
-        <v>494575886.38999999</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+        <v>8</v>
+      </c>
+      <c r="G22" s="5"/>
+    </row>
+    <row r="23" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>2026</v>
       </c>
-      <c r="B23" s="3">
-        <v>4</v>
+      <c r="B23" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="C23" s="3">
         <v>9999</v>
@@ -947,17 +978,19 @@
         <v>7</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G23" s="5">
-        <v>494575886.38999999</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2"/>
+        <v>12551122.09</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" s="1" customFormat="1" ht="28.7" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
--- a/upload/contabancaria.xlsx
+++ b/upload/contabancaria.xlsx
@@ -9,17 +9,25 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8430"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11130"/>
   </bookViews>
   <sheets>
-    <sheet name="contabacaria" sheetId="2" r:id="rId1"/>
+    <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="27">
+  <si>
+    <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+  </si>
   <si>
     <t>Ano de Exercício</t>
   </si>
@@ -37,6 +45,12 @@
   </si>
   <si>
     <t>Classificação Receita - Descrição</t>
+  </si>
+  <si>
+    <t>Fonte Recurso - Código</t>
+  </si>
+  <si>
+    <t>Fonte Recurso - Descrição</t>
   </si>
   <si>
     <t>Dezembro</t>
@@ -98,13 +112,15 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,###,###,###,###,##0.00"/>
+    <numFmt numFmtId="165" formatCode="#,###,###,###,###,##0.00"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
@@ -121,13 +137,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFF7F7F7"/>
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF7F7F7"/>
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
@@ -161,19 +177,19 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -456,541 +472,677 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G24"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:I24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="15.28515625" customWidth="1"/>
     <col min="3" max="4" width="10.7109375" customWidth="1"/>
-    <col min="5" max="7" width="44.5703125" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="5" max="9" width="44.5703125" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="1:9" s="2" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" s="2" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
         <v>2024</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C2" s="3">
         <v>9999</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="5">
+        <v>13</v>
+      </c>
+      <c r="G2" s="3">
+        <v>80</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="I2" s="5">
         <v>310515903.98000002</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" s="2" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>2024</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C3" s="3">
         <v>9999</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="3">
+        <v>80</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>310515903.98000002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" s="2" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="3">
+        <v>9999</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="3">
+        <v>80</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>2995148.47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" s="2" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="3">
+        <v>9999</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="3">
+        <v>80</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>14845558.060000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" s="2" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="G3" s="5">
-        <v>310515903.98000002</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="3">
-        <v>2025</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="3">
-        <v>9999</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" s="5">
-        <v>2995148.47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="3">
-        <v>2025</v>
-      </c>
-      <c r="B5" s="4" t="s">
+      <c r="C6" s="3">
+        <v>9999</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="3">
+        <v>80</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>27910418.219999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" s="2" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="3">
+        <v>9999</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="3">
+        <v>80</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>3083631.22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" s="2" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="3">
+        <v>9999</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="3">
-        <v>9999</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="G5" s="5">
-        <v>14845558.060000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="3">
-        <v>2025</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="3">
-        <v>9999</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="G6" s="5">
-        <v>27910418.219999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="3">
-        <v>2025</v>
-      </c>
-      <c r="B7" s="4" t="s">
+      <c r="G8" s="3">
+        <v>80</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5"/>
+    </row>
+    <row r="9" spans="1:9" s="2" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="3">
+        <v>9999</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="3">
+        <v>80</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5"/>
+    </row>
+    <row r="10" spans="1:9" s="2" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="3">
+        <v>9999</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="3">
+        <v>80</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>10803651.24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" s="2" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="3">
+        <v>9999</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="3">
-        <v>9999</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="G7" s="5">
-        <v>3083631.22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="3">
-        <v>2025</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="3">
-        <v>9999</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="5"/>
-    </row>
-    <row r="9" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="3">
-        <v>2025</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="3">
-        <v>9999</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="G9" s="5"/>
-    </row>
-    <row r="10" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="3">
-        <v>2025</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="3">
-        <v>9999</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="G10" s="5">
-        <v>10803651.24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="3">
-        <v>2025</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="3">
-        <v>9999</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>11</v>
-      </c>
       <c r="F11" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="5">
+        <v>13</v>
+      </c>
+      <c r="G11" s="3">
+        <v>80</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
         <v>846091078.27999997</v>
       </c>
     </row>
-    <row r="12" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" s="2" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>2025</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C12" s="3">
         <v>9999</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="G12" s="5">
+        <v>11</v>
+      </c>
+      <c r="G12" s="3">
+        <v>80</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
         <v>846091078.27999997</v>
       </c>
     </row>
-    <row r="13" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" s="2" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>2025</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C13" s="3">
         <v>9999</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="G13" s="5">
+        <v>11</v>
+      </c>
+      <c r="G13" s="3">
+        <v>80</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
         <v>3326424.56</v>
       </c>
     </row>
-    <row r="14" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" s="2" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>2025</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C14" s="3">
         <v>9999</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="G14" s="5">
+        <v>11</v>
+      </c>
+      <c r="G14" s="3">
+        <v>80</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
         <v>3043139.48</v>
       </c>
     </row>
-    <row r="15" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" s="2" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>2025</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C15" s="3">
         <v>9999</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="G15" s="5">
+        <v>11</v>
+      </c>
+      <c r="G15" s="3">
+        <v>80</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
         <v>15387953.630000001</v>
       </c>
     </row>
-    <row r="16" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" s="2" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>2025</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C16" s="3">
         <v>9999</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="G16" s="5">
+        <v>11</v>
+      </c>
+      <c r="G16" s="3">
+        <v>80</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
         <v>14539798.82</v>
       </c>
     </row>
-    <row r="17" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" s="2" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>2025</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C17" s="3">
         <v>9999</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="G17" s="5">
+        <v>11</v>
+      </c>
+      <c r="G17" s="3">
+        <v>80</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
         <v>13717383.76</v>
       </c>
     </row>
-    <row r="18" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" s="2" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>2026</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C18" s="3">
         <v>9999</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G18" s="5">
+        <v>13</v>
+      </c>
+      <c r="G18" s="3">
+        <v>80</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="I18" s="5">
         <v>494575886.38999999</v>
       </c>
     </row>
-    <row r="19" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" s="2" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>2026</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C19" s="3">
         <v>9999</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="G19" s="5">
+        <v>11</v>
+      </c>
+      <c r="G19" s="3">
+        <v>80</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="I19" s="5">
         <v>494575886.38999999</v>
       </c>
     </row>
-    <row r="20" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" s="2" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>2026</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C20" s="3">
         <v>9999</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="G20" s="5">
+        <v>11</v>
+      </c>
+      <c r="G20" s="3">
+        <v>80</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="I20" s="5">
         <v>14517354.300000001</v>
       </c>
     </row>
-    <row r="21" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" s="2" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>2026</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C21" s="3">
         <v>9999</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G21" s="5"/>
-    </row>
-    <row r="22" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+      <c r="G21" s="3">
+        <v>80</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="I21" s="5"/>
+    </row>
+    <row r="22" spans="1:9" s="2" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>2026</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C22" s="3">
         <v>9999</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="G22" s="5"/>
-    </row>
-    <row r="23" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="G22" s="3">
+        <v>80</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="I22" s="5"/>
+    </row>
+    <row r="23" spans="1:9" s="2" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>2026</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C23" s="3">
         <v>9999</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="G23" s="5">
+        <v>11</v>
+      </c>
+      <c r="G23" s="3">
+        <v>80</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="I23" s="5">
         <v>12551122.09</v>
       </c>
     </row>
-    <row r="24" spans="1:7" s="1" customFormat="1" ht="28.7" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="1:9" s="2" customFormat="1" ht="28.7" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
--- a/upload/contabancaria.xlsx
+++ b/upload/contabancaria.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Documents\transparencia-mg\portal_mariana\upload\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,53 +24,56 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="27">
+  <si>
+    <t>Ano de Exercício</t>
+  </si>
+  <si>
+    <t>Mês - Descritivo</t>
+  </si>
+  <si>
+    <t>Unidade Orçamentária - Código</t>
+  </si>
+  <si>
+    <t>Unidade Orçamentária - Nome</t>
+  </si>
+  <si>
+    <t>Classificação Receita - Descrição</t>
+  </si>
+  <si>
+    <t>Classificação Receita - Formatado</t>
+  </si>
+  <si>
+    <t>Fonte Recurso - Código</t>
+  </si>
+  <si>
+    <t>Fonte Recurso - Descrição</t>
+  </si>
+  <si>
+    <t>Valor Arrecadado Líquido</t>
+  </si>
+  <si>
+    <t>Dezembro</t>
+  </si>
+  <si>
+    <t>EMG - ADMINISTRACAO DIRETA</t>
+  </si>
+  <si>
+    <t>DEMAIS REC. CAPITAL - PRINC. - ROMPIMENTO DA BARRAGEM DE FUNDAO EM MARIANA - ACORDO JUDICIAL DE REPARACAO INTEGRAL E DEFINITIVA</t>
+  </si>
+  <si>
+    <t>2999.99.0.1.04.000</t>
+  </si>
   <si>
     <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
   </si>
   <si>
-    <t>Ano de Exercício</t>
-  </si>
-  <si>
-    <t>Mês - Descritivo</t>
-  </si>
-  <si>
-    <t>Unidade Orçamentária - Código</t>
-  </si>
-  <si>
-    <t>Unidade Orçamentária - Nome</t>
-  </si>
-  <si>
-    <t>Classificação Receita - Formatado</t>
-  </si>
-  <si>
-    <t>Classificação Receita - Descrição</t>
-  </si>
-  <si>
-    <t>Fonte Recurso - Código</t>
-  </si>
-  <si>
-    <t>Fonte Recurso - Descrição</t>
-  </si>
-  <si>
-    <t>Dezembro</t>
-  </si>
-  <si>
-    <t>EMG - ADMINISTRACAO DIRETA</t>
+    <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
   </si>
   <si>
     <t>1321.01.0.1.01.000</t>
   </si>
   <si>
-    <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
-  </si>
-  <si>
-    <t>2999.99.0.1.04.000</t>
-  </si>
-  <si>
-    <t>DEMAIS REC. CAPITAL - PRINC. - ROMPIMENTO DA BARRAGEM DE FUNDAO EM MARIANA - ACORDO JUDICIAL DE REPARACAO INTEGRAL E DEFINITIVA</t>
-  </si>
-  <si>
     <t>Abril</t>
   </si>
   <si>
@@ -102,9 +105,6 @@
   </si>
   <si>
     <t>Setembro</t>
-  </si>
-  <si>
-    <t>Valor Arrecadado Líquido</t>
   </si>
 </sst>
 </file>
@@ -112,7 +112,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="#,###,###,###,###,##0.00"/>
+    <numFmt numFmtId="164" formatCode="#,###,###,###,###,##0.00"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -189,7 +189,7 @@
     <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -472,7 +472,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -482,36 +482,36 @@
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="2" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>6</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" s="2" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
         <v>2024</v>
       </c>
@@ -525,22 +525,22 @@
         <v>10</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G2" s="3">
         <v>80</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I2" s="5">
         <v>310515903.98000002</v>
       </c>
     </row>
-    <row r="3" spans="1:9" s="2" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>2024</v>
       </c>
@@ -554,27 +554,27 @@
         <v>10</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G3" s="3">
         <v>80</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I3" s="5">
         <v>310515903.98000002</v>
       </c>
     </row>
-    <row r="4" spans="1:9" s="2" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>2025</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" s="3">
         <v>9999</v>
@@ -583,27 +583,27 @@
         <v>10</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G4" s="3">
         <v>80</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I4" s="5">
         <v>2995148.47</v>
       </c>
     </row>
-    <row r="5" spans="1:9" s="2" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>2025</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" s="3">
         <v>9999</v>
@@ -612,22 +612,22 @@
         <v>10</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G5" s="3">
         <v>80</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I5" s="5">
         <v>14845558.060000001</v>
       </c>
     </row>
-    <row r="6" spans="1:9" s="2" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>2025</v>
       </c>
@@ -641,27 +641,27 @@
         <v>10</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G6" s="3">
         <v>80</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I6" s="5">
         <v>27910418.219999999</v>
       </c>
     </row>
-    <row r="7" spans="1:9" s="2" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>2025</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" s="3">
         <v>9999</v>
@@ -670,27 +670,27 @@
         <v>10</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G7" s="3">
         <v>80</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I7" s="5">
         <v>3083631.22</v>
       </c>
     </row>
-    <row r="8" spans="1:9" s="2" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>2025</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" s="3">
         <v>9999</v>
@@ -699,25 +699,25 @@
         <v>10</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G8" s="3">
         <v>80</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I8" s="5"/>
     </row>
-    <row r="9" spans="1:9" s="2" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>2025</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" s="3">
         <v>9999</v>
@@ -726,25 +726,25 @@
         <v>10</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G9" s="3">
         <v>80</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I9" s="5"/>
     </row>
-    <row r="10" spans="1:9" s="2" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>2025</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" s="3">
         <v>9999</v>
@@ -753,27 +753,27 @@
         <v>10</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G10" s="3">
         <v>80</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I10" s="5">
         <v>10803651.24</v>
       </c>
     </row>
-    <row r="11" spans="1:9" s="2" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>2025</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11" s="3">
         <v>9999</v>
@@ -782,27 +782,27 @@
         <v>10</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G11" s="3">
         <v>80</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I11" s="5">
         <v>846091078.27999997</v>
       </c>
     </row>
-    <row r="12" spans="1:9" s="2" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>2025</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C12" s="3">
         <v>9999</v>
@@ -811,27 +811,27 @@
         <v>10</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G12" s="3">
         <v>80</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I12" s="5">
         <v>846091078.27999997</v>
       </c>
     </row>
-    <row r="13" spans="1:9" s="2" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>2025</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C13" s="3">
         <v>9999</v>
@@ -840,27 +840,27 @@
         <v>10</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G13" s="3">
         <v>80</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I13" s="5">
         <v>3326424.56</v>
       </c>
     </row>
-    <row r="14" spans="1:9" s="2" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>2025</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C14" s="3">
         <v>9999</v>
@@ -869,27 +869,27 @@
         <v>10</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G14" s="3">
         <v>80</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I14" s="5">
         <v>3043139.48</v>
       </c>
     </row>
-    <row r="15" spans="1:9" s="2" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>2025</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C15" s="3">
         <v>9999</v>
@@ -898,27 +898,27 @@
         <v>10</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G15" s="3">
         <v>80</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I15" s="5">
         <v>15387953.630000001</v>
       </c>
     </row>
-    <row r="16" spans="1:9" s="2" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>2025</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C16" s="3">
         <v>9999</v>
@@ -927,27 +927,27 @@
         <v>10</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G16" s="3">
         <v>80</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I16" s="5">
         <v>14539798.82</v>
       </c>
     </row>
-    <row r="17" spans="1:9" s="2" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>2025</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C17" s="3">
         <v>9999</v>
@@ -956,27 +956,27 @@
         <v>10</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G17" s="3">
         <v>80</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I17" s="5">
         <v>13717383.76</v>
       </c>
     </row>
-    <row r="18" spans="1:9" s="2" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>2026</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C18" s="3">
         <v>9999</v>
@@ -985,27 +985,27 @@
         <v>10</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G18" s="3">
         <v>80</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I18" s="5">
         <v>494575886.38999999</v>
       </c>
     </row>
-    <row r="19" spans="1:9" s="2" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>2026</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C19" s="3">
         <v>9999</v>
@@ -1014,27 +1014,27 @@
         <v>10</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G19" s="3">
         <v>80</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I19" s="5">
         <v>494575886.38999999</v>
       </c>
     </row>
-    <row r="20" spans="1:9" s="2" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>2026</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C20" s="3">
         <v>9999</v>
@@ -1043,27 +1043,27 @@
         <v>10</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G20" s="3">
         <v>80</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I20" s="5">
         <v>14517354.300000001</v>
       </c>
     </row>
-    <row r="21" spans="1:9" s="2" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>2026</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C21" s="3">
         <v>9999</v>
@@ -1072,25 +1072,25 @@
         <v>10</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G21" s="3">
         <v>80</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I21" s="5"/>
     </row>
-    <row r="22" spans="1:9" s="2" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>2026</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C22" s="3">
         <v>9999</v>
@@ -1099,20 +1099,20 @@
         <v>10</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G22" s="3">
         <v>80</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I22" s="5"/>
     </row>
-    <row r="23" spans="1:9" s="2" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>2026</v>
       </c>
@@ -1126,22 +1126,51 @@
         <v>10</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G23" s="3">
         <v>80</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I23" s="5">
+        <v>13997987.02</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A24" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="3">
+        <v>9999</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G24" s="3">
+        <v>80</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I24" s="5">
         <v>12551122.09</v>
       </c>
     </row>
-    <row r="24" spans="1:9" s="2" customFormat="1" ht="28.7" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/upload/contabancaria.xlsx
+++ b/upload/contabancaria.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11130"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8430"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>

--- a/upload/contabancaria.xlsx
+++ b/upload/contabancaria.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8430"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8400"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>

--- a/upload/contabancaria.xlsx
+++ b/upload/contabancaria.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1321,9 +1321,7 @@
           <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
         </is>
       </c>
-      <c r="I23" t="n">
-        <v>13997987.02</v>
-      </c>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1331,36 +1329,75 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>Maio</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>80</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>13997987.02</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>Março</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>9999</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>EMG - ADMINISTRACAO DIRETA</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>1321.01.0.1.01.000</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>80</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
+      <c r="C25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>80</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
         <v>12551122.09</v>
       </c>
     </row>

--- a/upload/contabancaria.xlsx
+++ b/upload/contabancaria.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1321,7 +1321,9 @@
           <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="n">
+        <v>18976150.59</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">

--- a/upload/contabancaria.xlsx
+++ b/upload/contabancaria.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/upload/contabancaria.xlsx
+++ b/upload/contabancaria.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1322,7 +1322,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>18976150.59</v>
+        <v>20616004.43</v>
       </c>
     </row>
     <row r="24">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>13997987.02</v>
+        <v>18976150.59</v>
       </c>
     </row>
     <row r="25">
@@ -1370,36 +1370,75 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>Maio</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>80</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>13997987.02</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>Março</t>
         </is>
       </c>
-      <c r="C25" t="n">
-        <v>9999</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>EMG - ADMINISTRACAO DIRETA</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>1321.01.0.1.01.000</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>80</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
+      <c r="C26" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>80</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
         <v>12551122.09</v>
       </c>
     </row>

--- a/upload/contabancaria.xlsx
+++ b/upload/contabancaria.xlsx
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>310515903.98</v>
+        <v>311247695.68</v>
       </c>
     </row>
     <row r="3">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>310515903.98</v>
+        <v>311247695.68</v>
       </c>
     </row>
     <row r="4">
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2995148.47</v>
+        <v>3002207.12</v>
       </c>
     </row>
     <row r="5">
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>14845558.06</v>
+        <v>14866422.81</v>
       </c>
     </row>
     <row r="6">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>27910418.22</v>
+        <v>27949646.04</v>
       </c>
     </row>
     <row r="7">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3083631.22</v>
+        <v>3090898.4</v>
       </c>
     </row>
     <row r="8">
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>10803651.24</v>
+        <v>10819505.67</v>
       </c>
     </row>
     <row r="11">
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>846091078.28</v>
+        <v>846972338.41</v>
       </c>
     </row>
     <row r="12">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>846091078.28</v>
+        <v>846972338.41</v>
       </c>
     </row>
     <row r="13">
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3326424.56</v>
+        <v>3334263.94</v>
       </c>
     </row>
     <row r="14">
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3043139.48</v>
+        <v>3050311.23</v>
       </c>
     </row>
     <row r="15">
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>15387953.63</v>
+        <v>15409580.69</v>
       </c>
     </row>
     <row r="16">
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>14539798.82</v>
+        <v>14560233.82</v>
       </c>
     </row>
     <row r="17">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>13717383.76</v>
+        <v>13736662.91</v>
       </c>
     </row>
     <row r="18">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>494575886.39</v>
+        <v>496313421.63</v>
       </c>
     </row>
     <row r="19">
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>494575886.39</v>
+        <v>496313421.63</v>
       </c>
     </row>
     <row r="20">
@@ -1209,7 +1209,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>14517354.3</v>
+        <v>14537788.73</v>
       </c>
     </row>
     <row r="21">
@@ -1322,7 +1322,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>20616004.43</v>
+        <v>20655908.62</v>
       </c>
     </row>
     <row r="24">
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>18976150.59</v>
+        <v>19013985.69</v>
       </c>
     </row>
     <row r="25">
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>13997987.02</v>
+        <v>14017776.05</v>
       </c>
     </row>
     <row r="26">
@@ -1439,7 +1439,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>12551122.09</v>
+        <v>12568823.22</v>
       </c>
     </row>
   </sheetData>

--- a/upload/contabancaria.xlsx
+++ b/upload/contabancaria.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,12 +494,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>DEMAIS REC. CAPITAL - PRINC. - ROMPIMENTO DA BARRAGEM DE FUNDAO EM MARIANA - ACORDO JUDICIAL DE REPARACAO INTEGRAL E DEFINITIVA</t>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2999.99.0.1.04.000</t>
+          <t>1321.01.0.1.01.000</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -516,11 +516,11 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>311247695.68</v>
+        <v>3002207.12</v>
       </c>
     </row>
     <row r="4">
@@ -559,7 +559,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>3002207.12</v>
+        <v>14866422.81</v>
       </c>
     </row>
     <row r="5">
@@ -598,7 +598,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>14866422.81</v>
+        <v>27949646.04</v>
       </c>
     </row>
     <row r="6">
@@ -637,7 +637,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>27949646.04</v>
+        <v>3090898.4</v>
       </c>
     </row>
     <row r="7">
@@ -676,7 +676,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -705,9 +705,7 @@
           <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
         </is>
       </c>
-      <c r="I7" t="n">
-        <v>3090898.4</v>
-      </c>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -715,7 +713,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -728,12 +726,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>DEMAIS REC. CAPITAL - PRINC. - ROMPIMENTO DA BARRAGEM DE FUNDAO EM MARIANA - ACORDO JUDICIAL DE REPARACAO INTEGRAL E DEFINITIVA</t>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2999.99.0.1.04.000</t>
+          <t>1321.01.0.1.01.000</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -744,7 +742,9 @@
           <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>10819505.67</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -752,7 +752,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -781,7 +781,9 @@
           <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="n">
+        <v>846972338.41</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -789,7 +791,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -819,7 +821,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>10819505.67</v>
+        <v>3334263.94</v>
       </c>
     </row>
     <row r="11">
@@ -828,7 +830,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -841,12 +843,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>DEMAIS REC. CAPITAL - PRINC. - ROMPIMENTO DA BARRAGEM DE FUNDAO EM MARIANA - ACORDO JUDICIAL DE REPARACAO INTEGRAL E DEFINITIVA</t>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2999.99.0.1.04.000</t>
+          <t>1321.01.0.1.01.000</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -858,7 +860,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>846972338.41</v>
+        <v>3050311.23</v>
       </c>
     </row>
     <row r="12">
@@ -867,7 +869,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -897,7 +899,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>846972338.41</v>
+        <v>15409580.69</v>
       </c>
     </row>
     <row r="13">
@@ -906,7 +908,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -936,7 +938,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3334263.94</v>
+        <v>14560233.82</v>
       </c>
     </row>
     <row r="14">
@@ -945,7 +947,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -975,16 +977,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3050311.23</v>
+        <v>13736662.91</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1014,16 +1016,16 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>15409580.69</v>
+        <v>496313421.63</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1053,16 +1055,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>14560233.82</v>
+        <v>14537788.73</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1091,9 +1093,7 @@
           <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>13736662.91</v>
-      </c>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>DEMAIS REC. CAPITAL - PRINC. - ROMPIMENTO DA BARRAGEM DE FUNDAO EM MARIANA - ACORDO JUDICIAL DE REPARACAO INTEGRAL E DEFINITIVA</t>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2999.99.0.1.04.000</t>
+          <t>1321.01.0.1.01.000</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>496313421.63</v>
+        <v>20655908.62</v>
       </c>
     </row>
     <row r="19">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>496313421.63</v>
+        <v>19013985.69</v>
       </c>
     </row>
     <row r="20">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1209,7 +1209,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>14537788.73</v>
+        <v>14017776.05</v>
       </c>
     </row>
     <row r="21">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1231,12 +1231,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>DEMAIS REC. CAPITAL - PRINC. - ROMPIMENTO DA BARRAGEM DE FUNDAO EM MARIANA - ACORDO JUDICIAL DE REPARACAO INTEGRAL E DEFINITIVA</t>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2999.99.0.1.04.000</t>
+          <t>1321.01.0.1.01.000</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -1247,198 +1247,7 @@
           <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Janeiro</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>9999</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>EMG - ADMINISTRACAO DIRETA</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>1321.01.0.1.01.000</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>80</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Julho</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>9999</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>EMG - ADMINISTRACAO DIRETA</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>1321.01.0.1.01.000</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>80</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>20655908.62</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Junho</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>9999</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>EMG - ADMINISTRACAO DIRETA</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>1321.01.0.1.01.000</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>80</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>19013985.69</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Maio</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>9999</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>EMG - ADMINISTRACAO DIRETA</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>1321.01.0.1.01.000</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>80</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>14017776.05</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Março</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>9999</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>EMG - ADMINISTRACAO DIRETA</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>1321.01.0.1.01.000</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>80</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
+      <c r="I21" t="n">
         <v>12568823.22</v>
       </c>
     </row>

--- a/upload/contabancaria.xlsx
+++ b/upload/contabancaria.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>311247695.68</v>
+        <v>4600135.94</v>
       </c>
     </row>
     <row r="3">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>3002207.12</v>
+        <v>7188079.76</v>
       </c>
     </row>
     <row r="4">
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>14866422.81</v>
+        <v>22427853.45</v>
       </c>
     </row>
     <row r="5">
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>27949646.04</v>
+        <v>40499522.78</v>
       </c>
     </row>
     <row r="6">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3090898.4</v>
+        <v>7398834.46</v>
       </c>
     </row>
     <row r="7">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>10819505.67</v>
+        <v>16983866.92</v>
       </c>
     </row>
     <row r="9">
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>846972338.41</v>
+        <v>8609495.35</v>
       </c>
     </row>
     <row r="10">
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3334263.94</v>
+        <v>7970149.65</v>
       </c>
     </row>
     <row r="11">
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3050311.23</v>
+        <v>7303253.83</v>
       </c>
     </row>
     <row r="12">
@@ -899,7 +899,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>15409580.69</v>
+        <v>22928693.47</v>
       </c>
     </row>
     <row r="13">
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>14560233.82</v>
+        <v>21837506.46</v>
       </c>
     </row>
     <row r="14">
@@ -977,7 +977,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>13736662.91</v>
+        <v>20665598.17</v>
       </c>
     </row>
     <row r="15">
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>496313421.63</v>
+        <v>20910819.96</v>
       </c>
     </row>
     <row r="16">
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>14537788.73</v>
+        <v>20377508.26</v>
       </c>
     </row>
     <row r="17">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>20655908.62</v>
+        <v>33435461.07</v>
       </c>
     </row>
     <row r="19">
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>19013985.69</v>
+        <v>31794430.57</v>
       </c>
     </row>
     <row r="20">
@@ -1209,7 +1209,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>14017776.05</v>
+        <v>18942112.58</v>
       </c>
     </row>
     <row r="21">
@@ -1248,7 +1248,24 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>12568823.22</v>
+        <v>17183256.57</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Soma:</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>331056579.25</v>
       </c>
     </row>
   </sheetData>

--- a/upload/contabancaria.xlsx
+++ b/upload/contabancaria.xlsx
@@ -1054,7 +1054,9 @@
           <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="n">
+        <v>36273133.75</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1302,7 +1304,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>331056579.25</v>
+        <v>367329713</v>
       </c>
     </row>
   </sheetData>

--- a/upload/contabancaria.xlsx
+++ b/upload/contabancaria.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:J181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,25 +451,30 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Classificação Receita - Formatado</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Classificação Receita - Descrição</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Classificação Receita - Formatado</t>
-        </is>
-      </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Código Iniciativa</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Fonte Recurso - Código</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Fonte Recurso - Descrição</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Valor Arrecadado Líquido</t>
         </is>
@@ -479,10 +484,8 @@
       <c r="A2" t="n">
         <v>2024</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Dezembro</t>
-        </is>
+      <c r="B2" t="n">
+        <v>12</v>
       </c>
       <c r="C2" t="n">
         <v>9999</v>
@@ -494,34 +497,35 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+          <t>1321.01.0.1.01.000</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1321.01.0.1.01.000</t>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>80</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>4600135.94</v>
+        <v>9445683</v>
+      </c>
+      <c r="H2" t="n">
+        <v>80</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>151149.27</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Abril</t>
-        </is>
+        <v>2024</v>
+      </c>
+      <c r="B3" t="n">
+        <v>12</v>
       </c>
       <c r="C3" t="n">
         <v>9999</v>
@@ -533,34 +537,35 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+          <t>1321.01.0.1.01.000</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1321.01.0.1.01.000</t>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>80</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>7188079.76</v>
+        <v>9445684</v>
+      </c>
+      <c r="H3" t="n">
+        <v>80</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>4518.97</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Agosto</t>
-        </is>
+        <v>2024</v>
+      </c>
+      <c r="B4" t="n">
+        <v>12</v>
       </c>
       <c r="C4" t="n">
         <v>9999</v>
@@ -572,34 +577,35 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+          <t>1321.01.0.1.01.000</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1321.01.0.1.01.000</t>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>80</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>22427853.45</v>
+        <v>9445703</v>
+      </c>
+      <c r="H4" t="n">
+        <v>80</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>19834.35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Dezembro</t>
-        </is>
+        <v>2024</v>
+      </c>
+      <c r="B5" t="n">
+        <v>12</v>
       </c>
       <c r="C5" t="n">
         <v>9999</v>
@@ -611,34 +617,35 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+          <t>1321.01.0.1.01.000</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1321.01.0.1.01.000</t>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>80</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>40499522.78</v>
+        <v>9445716</v>
+      </c>
+      <c r="H5" t="n">
+        <v>80</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>2678116.29</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Fevereiro</t>
-        </is>
+        <v>2024</v>
+      </c>
+      <c r="B6" t="n">
+        <v>12</v>
       </c>
       <c r="C6" t="n">
         <v>9999</v>
@@ -650,34 +657,35 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+          <t>1321.01.0.1.01.000</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1321.01.0.1.01.000</t>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>80</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>7398834.46</v>
+        <v>9445718</v>
+      </c>
+      <c r="H6" t="n">
+        <v>80</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>251727.57</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Janeiro</t>
-        </is>
+        <v>2024</v>
+      </c>
+      <c r="B7" t="n">
+        <v>12</v>
       </c>
       <c r="C7" t="n">
         <v>9999</v>
@@ -689,32 +697,35 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+          <t>1321.01.0.1.01.000</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1321.01.0.1.01.000</t>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>80</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+        <v>9445719</v>
+      </c>
+      <c r="H7" t="n">
+        <v>80</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>392585.24</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Julho</t>
-        </is>
+        <v>2024</v>
+      </c>
+      <c r="B8" t="n">
+        <v>12</v>
       </c>
       <c r="C8" t="n">
         <v>9999</v>
@@ -726,34 +737,35 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+          <t>1321.01.0.1.01.000</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1321.01.0.1.01.000</t>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>80</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>16983866.92</v>
+        <v>9445721</v>
+      </c>
+      <c r="H8" t="n">
+        <v>80</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1040068.45</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Junho</t>
-        </is>
+        <v>2024</v>
+      </c>
+      <c r="B9" t="n">
+        <v>12</v>
       </c>
       <c r="C9" t="n">
         <v>9999</v>
@@ -765,34 +777,35 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+          <t>1321.01.0.1.01.000</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1321.01.0.1.01.000</t>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>80</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>8609495.35</v>
+        <v>9445763</v>
+      </c>
+      <c r="H9" t="n">
+        <v>80</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>62135.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>2025</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Maio</t>
-        </is>
+      <c r="B10" t="n">
+        <v>1</v>
       </c>
       <c r="C10" t="n">
         <v>9999</v>
@@ -804,34 +817,35 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+          <t>1321.01.0.1.01.000</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1321.01.0.1.01.000</t>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>80</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>7970149.65</v>
+        <v>9445683</v>
+      </c>
+      <c r="H10" t="n">
+        <v>80</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>243070.91</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>2025</v>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Março</t>
-        </is>
+      <c r="B11" t="n">
+        <v>1</v>
       </c>
       <c r="C11" t="n">
         <v>9999</v>
@@ -843,34 +857,35 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+          <t>1321.01.0.1.01.000</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1321.01.0.1.01.000</t>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>80</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>7303253.83</v>
+        <v>9445684</v>
+      </c>
+      <c r="H11" t="n">
+        <v>80</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>7267.18</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>2025</v>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Novembro</t>
-        </is>
+      <c r="B12" t="n">
+        <v>1</v>
       </c>
       <c r="C12" t="n">
         <v>9999</v>
@@ -882,34 +897,35 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+          <t>1321.01.0.1.01.000</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1321.01.0.1.01.000</t>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>80</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>22928693.47</v>
+        <v>9445703</v>
+      </c>
+      <c r="H12" t="n">
+        <v>80</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>31896.62</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>2025</v>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Outubro</t>
-        </is>
+      <c r="B13" t="n">
+        <v>1</v>
       </c>
       <c r="C13" t="n">
         <v>9999</v>
@@ -921,34 +937,35 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+          <t>1321.01.0.1.01.000</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1321.01.0.1.01.000</t>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>80</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>21837506.46</v>
+        <v>9445716</v>
+      </c>
+      <c r="H13" t="n">
+        <v>80</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>4306816.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>2025</v>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Setembro</t>
-        </is>
+      <c r="B14" t="n">
+        <v>1</v>
       </c>
       <c r="C14" t="n">
         <v>9999</v>
@@ -960,34 +977,35 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+          <t>1321.01.0.1.01.000</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1321.01.0.1.01.000</t>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>80</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>20665598.17</v>
+        <v>9445718</v>
+      </c>
+      <c r="H14" t="n">
+        <v>80</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>404816.01</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Abril</t>
-        </is>
+        <v>2025</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
       </c>
       <c r="C15" t="n">
         <v>9999</v>
@@ -999,34 +1017,35 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+          <t>1321.01.0.1.01.000</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1321.01.0.1.01.000</t>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>80</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>20910819.96</v>
+        <v>9445719</v>
+      </c>
+      <c r="H15" t="n">
+        <v>80</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>631336.47</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Agosto</t>
-        </is>
+        <v>2025</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
       </c>
       <c r="C16" t="n">
         <v>9999</v>
@@ -1038,34 +1057,35 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+          <t>1321.01.0.1.01.000</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1321.01.0.1.01.000</t>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>80</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>36273133.75</v>
+        <v>9445721</v>
+      </c>
+      <c r="H16" t="n">
+        <v>80</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>1672587.45</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Fevereiro</t>
-        </is>
+        <v>2025</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
       </c>
       <c r="C17" t="n">
         <v>9999</v>
@@ -1077,34 +1097,35 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+          <t>1321.01.0.1.01.000</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1321.01.0.1.01.000</t>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>80</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>20377508.26</v>
+        <v>9445763</v>
+      </c>
+      <c r="H17" t="n">
+        <v>80</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>99923.75999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Janeiro</t>
-        </is>
+        <v>2025</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
       </c>
       <c r="C18" t="n">
         <v>9999</v>
@@ -1116,32 +1137,35 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+          <t>1321.01.0.1.01.000</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1321.01.0.1.01.000</t>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>80</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+        <v>9447774</v>
+      </c>
+      <c r="H18" t="n">
+        <v>80</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>1119.76</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Julho</t>
-        </is>
+        <v>2025</v>
+      </c>
+      <c r="B19" t="n">
+        <v>2</v>
       </c>
       <c r="C19" t="n">
         <v>9999</v>
@@ -1153,34 +1177,35 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+          <t>1321.01.0.1.01.000</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1321.01.0.1.01.000</t>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>80</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>33435461.07</v>
+        <v>9445683</v>
+      </c>
+      <c r="H19" t="n">
+        <v>80</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>239879.08</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Junho</t>
-        </is>
+        <v>2025</v>
+      </c>
+      <c r="B20" t="n">
+        <v>2</v>
       </c>
       <c r="C20" t="n">
         <v>9999</v>
@@ -1192,34 +1217,35 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+          <t>1321.01.0.1.01.000</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1321.01.0.1.01.000</t>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>80</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>31794430.57</v>
+        <v>9445684</v>
+      </c>
+      <c r="H20" t="n">
+        <v>80</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>7171.75</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Maio</t>
-        </is>
+        <v>2025</v>
+      </c>
+      <c r="B21" t="n">
+        <v>2</v>
       </c>
       <c r="C21" t="n">
         <v>9999</v>
@@ -1231,79 +1257,6400 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+          <t>1321.01.0.1.01.000</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1321.01.0.1.01.000</t>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>80</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>18942112.58</v>
+        <v>9445703</v>
+      </c>
+      <c r="H21" t="n">
+        <v>80</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>31477.77</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B22" t="n">
+        <v>2</v>
+      </c>
+      <c r="C22" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>9445716</v>
+      </c>
+      <c r="H22" t="n">
+        <v>80</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>4250262.74</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B23" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>9445718</v>
+      </c>
+      <c r="H23" t="n">
+        <v>80</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>399500.3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B24" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>9445719</v>
+      </c>
+      <c r="H24" t="n">
+        <v>80</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>623046.28</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B25" t="n">
+        <v>2</v>
+      </c>
+      <c r="C25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>9445721</v>
+      </c>
+      <c r="H25" t="n">
+        <v>80</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>1650624.42</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B26" t="n">
+        <v>2</v>
+      </c>
+      <c r="C26" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>9445763</v>
+      </c>
+      <c r="H26" t="n">
+        <v>80</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>98611.63</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B27" t="n">
+        <v>2</v>
+      </c>
+      <c r="C27" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>9447774</v>
+      </c>
+      <c r="H27" t="n">
+        <v>80</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>2679.86</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B28" t="n">
+        <v>3</v>
+      </c>
+      <c r="C28" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>9445683</v>
+      </c>
+      <c r="H28" t="n">
+        <v>80</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>236096.14</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B29" t="n">
+        <v>3</v>
+      </c>
+      <c r="C29" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>9445684</v>
+      </c>
+      <c r="H29" t="n">
+        <v>80</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>7058.65</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B30" t="n">
+        <v>3</v>
+      </c>
+      <c r="C30" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>9445703</v>
+      </c>
+      <c r="H30" t="n">
+        <v>80</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>30981.38</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B31" t="n">
+        <v>3</v>
+      </c>
+      <c r="C31" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>9445716</v>
+      </c>
+      <c r="H31" t="n">
+        <v>80</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>4183235.04</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B32" t="n">
+        <v>3</v>
+      </c>
+      <c r="C32" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>9445718</v>
+      </c>
+      <c r="H32" t="n">
+        <v>80</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>393200.09</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B33" t="n">
+        <v>3</v>
+      </c>
+      <c r="C33" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>9445719</v>
+      </c>
+      <c r="H33" t="n">
+        <v>80</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>613220.6899999999</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>9445721</v>
+      </c>
+      <c r="H34" t="n">
+        <v>80</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>1624593.66</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B35" t="n">
+        <v>3</v>
+      </c>
+      <c r="C35" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>9445763</v>
+      </c>
+      <c r="H35" t="n">
+        <v>80</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>97056.50999999999</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B36" t="n">
+        <v>3</v>
+      </c>
+      <c r="C36" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>9447774</v>
+      </c>
+      <c r="H36" t="n">
+        <v>80</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>2637.6</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B37" t="n">
+        <v>4</v>
+      </c>
+      <c r="C37" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>9445683</v>
+      </c>
+      <c r="H37" t="n">
+        <v>80</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>262209.38</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B38" t="n">
+        <v>4</v>
+      </c>
+      <c r="C38" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>9445684</v>
+      </c>
+      <c r="H38" t="n">
+        <v>80</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>7839.38</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B39" t="n">
+        <v>4</v>
+      </c>
+      <c r="C39" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>9445703</v>
+      </c>
+      <c r="H39" t="n">
+        <v>80</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>34408.04</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B40" t="n">
+        <v>4</v>
+      </c>
+      <c r="C40" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>9445716</v>
+      </c>
+      <c r="H40" t="n">
+        <v>80</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>4632956.38</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B41" t="n">
+        <v>4</v>
+      </c>
+      <c r="C41" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>9445718</v>
+      </c>
+      <c r="H41" t="n">
+        <v>80</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>436689.68</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B42" t="n">
+        <v>4</v>
+      </c>
+      <c r="C42" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>9445719</v>
+      </c>
+      <c r="H42" t="n">
+        <v>80</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>681045.49</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B43" t="n">
+        <v>4</v>
+      </c>
+      <c r="C43" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>9445721</v>
+      </c>
+      <c r="H43" t="n">
+        <v>80</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>1804280.6</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B44" t="n">
+        <v>4</v>
+      </c>
+      <c r="C44" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>9445763</v>
+      </c>
+      <c r="H44" t="n">
+        <v>80</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>107791.37</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B45" t="n">
+        <v>4</v>
+      </c>
+      <c r="C45" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>9447774</v>
+      </c>
+      <c r="H45" t="n">
+        <v>80</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>2929.33</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B46" t="n">
+        <v>5</v>
+      </c>
+      <c r="C46" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>9445683</v>
+      </c>
+      <c r="H46" t="n">
+        <v>80</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>285404.82</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B47" t="n">
+        <v>5</v>
+      </c>
+      <c r="C47" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>9445684</v>
+      </c>
+      <c r="H47" t="n">
+        <v>80</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>8532.860000000001</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B48" t="n">
+        <v>5</v>
+      </c>
+      <c r="C48" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>9445703</v>
+      </c>
+      <c r="H48" t="n">
+        <v>80</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>37451.84</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B49" t="n">
+        <v>5</v>
+      </c>
+      <c r="C49" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>9445716</v>
+      </c>
+      <c r="H49" t="n">
+        <v>80</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>4977088.79</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B50" t="n">
+        <v>5</v>
+      </c>
+      <c r="C50" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>9445718</v>
+      </c>
+      <c r="H50" t="n">
+        <v>80</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>475319.93</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B51" t="n">
+        <v>5</v>
+      </c>
+      <c r="C51" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>9445719</v>
+      </c>
+      <c r="H51" t="n">
+        <v>80</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>741291.84</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B52" t="n">
+        <v>5</v>
+      </c>
+      <c r="C52" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>9445721</v>
+      </c>
+      <c r="H52" t="n">
+        <v>80</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>1963890.04</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B53" t="n">
+        <v>5</v>
+      </c>
+      <c r="C53" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>9445763</v>
+      </c>
+      <c r="H53" t="n">
+        <v>80</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>117326.77</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B54" t="n">
+        <v>5</v>
+      </c>
+      <c r="C54" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>9447774</v>
+      </c>
+      <c r="H54" t="n">
+        <v>80</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>3188.46</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B55" t="n">
+        <v>6</v>
+      </c>
+      <c r="C55" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>9445683</v>
+      </c>
+      <c r="H55" t="n">
+        <v>80</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>1306332.23</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B56" t="n">
+        <v>6</v>
+      </c>
+      <c r="C56" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>9445684</v>
+      </c>
+      <c r="H56" t="n">
+        <v>80</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>15854.43</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B57" t="n">
+        <v>6</v>
+      </c>
+      <c r="C57" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>9445703</v>
+      </c>
+      <c r="H57" t="n">
+        <v>80</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>69587.27</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B58" t="n">
+        <v>6</v>
+      </c>
+      <c r="C58" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>9445716</v>
+      </c>
+      <c r="H58" t="n">
+        <v>80</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>6161252.34</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B59" t="n">
+        <v>6</v>
+      </c>
+      <c r="C59" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>9445718</v>
+      </c>
+      <c r="H59" t="n">
+        <v>80</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>1704298.8</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B60" t="n">
+        <v>6</v>
+      </c>
+      <c r="C60" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>9445719</v>
+      </c>
+      <c r="H60" t="n">
+        <v>80</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>2002424.2</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B61" t="n">
+        <v>6</v>
+      </c>
+      <c r="C61" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>9445721</v>
+      </c>
+      <c r="H61" t="n">
+        <v>80</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>2628119.6</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B62" t="n">
+        <v>6</v>
+      </c>
+      <c r="C62" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>9445763</v>
+      </c>
+      <c r="H62" t="n">
+        <v>80</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>3092889.14</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B63" t="n">
+        <v>6</v>
+      </c>
+      <c r="C63" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>9447774</v>
+      </c>
+      <c r="H63" t="n">
+        <v>80</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>3108.91</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B64" t="n">
+        <v>7</v>
+      </c>
+      <c r="C64" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>9445683</v>
+      </c>
+      <c r="H64" t="n">
+        <v>80</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>1838667.82</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B65" t="n">
+        <v>7</v>
+      </c>
+      <c r="C65" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>9445684</v>
+      </c>
+      <c r="H65" t="n">
+        <v>80</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>20864.75</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B66" t="n">
+        <v>7</v>
+      </c>
+      <c r="C66" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>9445703</v>
+      </c>
+      <c r="H66" t="n">
+        <v>80</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>91578.25999999999</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B67" t="n">
+        <v>7</v>
+      </c>
+      <c r="C67" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>9445716</v>
+      </c>
+      <c r="H67" t="n">
+        <v>80</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>7557772.81</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B68" t="n">
+        <v>7</v>
+      </c>
+      <c r="C68" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>9445718</v>
+      </c>
+      <c r="H68" t="n">
+        <v>80</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>2369344.48</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B69" t="n">
+        <v>7</v>
+      </c>
+      <c r="C69" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>9445719</v>
+      </c>
+      <c r="H69" t="n">
+        <v>80</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>2731490.2</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B70" t="n">
+        <v>7</v>
+      </c>
+      <c r="C70" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>9445721</v>
+      </c>
+      <c r="H70" t="n">
+        <v>80</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>3301444.9</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B71" t="n">
+        <v>7</v>
+      </c>
+      <c r="C71" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>9445763</v>
+      </c>
+      <c r="H71" t="n">
+        <v>80</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>4513032.4</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B72" t="n">
+        <v>7</v>
+      </c>
+      <c r="C72" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>9447774</v>
+      </c>
+      <c r="H72" t="n">
+        <v>80</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>3657.83</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B73" t="n">
+        <v>8</v>
+      </c>
+      <c r="C73" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>9445683</v>
+      </c>
+      <c r="H73" t="n">
+        <v>80</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>1698939.98</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B74" t="n">
+        <v>8</v>
+      </c>
+      <c r="C74" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>9445684</v>
+      </c>
+      <c r="H74" t="n">
+        <v>80</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>19279.15</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B75" t="n">
+        <v>8</v>
+      </c>
+      <c r="C75" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>9445703</v>
+      </c>
+      <c r="H75" t="n">
+        <v>80</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>84618.84</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B76" t="n">
+        <v>8</v>
+      </c>
+      <c r="C76" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>9445716</v>
+      </c>
+      <c r="H76" t="n">
+        <v>80</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>6925555.41</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B77" t="n">
+        <v>8</v>
+      </c>
+      <c r="C77" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>9445718</v>
+      </c>
+      <c r="H77" t="n">
+        <v>80</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>2189288.35</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B78" t="n">
+        <v>8</v>
+      </c>
+      <c r="C78" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>9445719</v>
+      </c>
+      <c r="H78" t="n">
+        <v>80</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>2523913.16</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B79" t="n">
+        <v>8</v>
+      </c>
+      <c r="C79" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>9445721</v>
+      </c>
+      <c r="H79" t="n">
+        <v>80</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>3050554.69</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B80" t="n">
+        <v>8</v>
+      </c>
+      <c r="C80" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>9445763</v>
+      </c>
+      <c r="H80" t="n">
+        <v>80</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>4170068.74</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B81" t="n">
+        <v>8</v>
+      </c>
+      <c r="C81" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>9447774</v>
+      </c>
+      <c r="H81" t="n">
+        <v>80</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>3379.85</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B82" t="n">
+        <v>9</v>
+      </c>
+      <c r="C82" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>9445683</v>
+      </c>
+      <c r="H82" t="n">
+        <v>80</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>1800798.61</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B83" t="n">
+        <v>9</v>
+      </c>
+      <c r="C83" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>9445684</v>
+      </c>
+      <c r="H83" t="n">
+        <v>80</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>20435</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B84" t="n">
+        <v>9</v>
+      </c>
+      <c r="C84" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>9445703</v>
+      </c>
+      <c r="H84" t="n">
+        <v>80</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>89692.09</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B85" t="n">
+        <v>9</v>
+      </c>
+      <c r="C85" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>9445716</v>
+      </c>
+      <c r="H85" t="n">
+        <v>80</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>7273690.16</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B86" t="n">
+        <v>9</v>
+      </c>
+      <c r="C86" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>9445718</v>
+      </c>
+      <c r="H86" t="n">
+        <v>80</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>2320545.43</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B87" t="n">
+        <v>9</v>
+      </c>
+      <c r="C87" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>9445719</v>
+      </c>
+      <c r="H87" t="n">
+        <v>80</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>2675232.4</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B88" t="n">
+        <v>9</v>
+      </c>
+      <c r="C88" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>9445721</v>
+      </c>
+      <c r="H88" t="n">
+        <v>80</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>3233448.32</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B89" t="n">
+        <v>9</v>
+      </c>
+      <c r="C89" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>9445763</v>
+      </c>
+      <c r="H89" t="n">
+        <v>80</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>4420081.97</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B90" t="n">
+        <v>9</v>
+      </c>
+      <c r="C90" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>9447774</v>
+      </c>
+      <c r="H90" t="n">
+        <v>80</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>3582.48</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B91" t="n">
+        <v>10</v>
+      </c>
+      <c r="C91" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G91" t="n">
+        <v>9445683</v>
+      </c>
+      <c r="H91" t="n">
+        <v>80</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>1905845.17</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B92" t="n">
+        <v>10</v>
+      </c>
+      <c r="C92" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>9445684</v>
+      </c>
+      <c r="H92" t="n">
+        <v>80</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>21627.06</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B93" t="n">
+        <v>10</v>
+      </c>
+      <c r="C93" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G93" t="n">
+        <v>9445703</v>
+      </c>
+      <c r="H93" t="n">
+        <v>80</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>94924.14</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B94" t="n">
+        <v>10</v>
+      </c>
+      <c r="C94" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>9445716</v>
+      </c>
+      <c r="H94" t="n">
+        <v>80</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>7515515.44</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B95" t="n">
+        <v>10</v>
+      </c>
+      <c r="C95" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>9445718</v>
+      </c>
+      <c r="H95" t="n">
+        <v>80</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>2455910.57</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B96" t="n">
+        <v>10</v>
+      </c>
+      <c r="C96" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>9445719</v>
+      </c>
+      <c r="H96" t="n">
+        <v>80</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>2831287.6</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B97" t="n">
+        <v>10</v>
+      </c>
+      <c r="C97" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>9445721</v>
+      </c>
+      <c r="H97" t="n">
+        <v>80</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>3422066.11</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B98" t="n">
+        <v>10</v>
+      </c>
+      <c r="C98" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>9445763</v>
+      </c>
+      <c r="H98" t="n">
+        <v>80</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>4677920.04</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B99" t="n">
+        <v>10</v>
+      </c>
+      <c r="C99" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>9447774</v>
+      </c>
+      <c r="H99" t="n">
+        <v>80</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J99" t="n">
+        <v>3597.34</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B100" t="n">
+        <v>11</v>
+      </c>
+      <c r="C100" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>9445683</v>
+      </c>
+      <c r="H100" t="n">
+        <v>80</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J100" t="n">
+        <v>1592387.71</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B101" t="n">
+        <v>11</v>
+      </c>
+      <c r="C101" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>9445684</v>
+      </c>
+      <c r="H101" t="n">
+        <v>80</v>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J101" t="n">
+        <v>18070.01</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B102" t="n">
+        <v>11</v>
+      </c>
+      <c r="C102" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
+        <v>9445703</v>
+      </c>
+      <c r="H102" t="n">
+        <v>80</v>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J102" t="n">
+        <v>79311.8</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B103" t="n">
+        <v>11</v>
+      </c>
+      <c r="C103" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>9445716</v>
+      </c>
+      <c r="H103" t="n">
+        <v>80</v>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>6048434.22</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B104" t="n">
+        <v>11</v>
+      </c>
+      <c r="C104" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>9445718</v>
+      </c>
+      <c r="H104" t="n">
+        <v>80</v>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
+        <v>2051982.94</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B105" t="n">
+        <v>11</v>
+      </c>
+      <c r="C105" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>9445719</v>
+      </c>
+      <c r="H105" t="n">
+        <v>80</v>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v>2365621.11</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B106" t="n">
+        <v>11</v>
+      </c>
+      <c r="C106" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>9445721</v>
+      </c>
+      <c r="H106" t="n">
+        <v>80</v>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J106" t="n">
+        <v>2859233.3</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B107" t="n">
+        <v>11</v>
+      </c>
+      <c r="C107" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>9445763</v>
+      </c>
+      <c r="H107" t="n">
+        <v>80</v>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J107" t="n">
+        <v>3908534.89</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B108" t="n">
+        <v>11</v>
+      </c>
+      <c r="C108" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>9447774</v>
+      </c>
+      <c r="H108" t="n">
+        <v>80</v>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J108" t="n">
+        <v>1313.16</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B109" t="n">
+        <v>12</v>
+      </c>
+      <c r="C109" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>9445683</v>
+      </c>
+      <c r="H109" t="n">
+        <v>80</v>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J109" t="n">
+        <v>1864493.6</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B110" t="n">
+        <v>12</v>
+      </c>
+      <c r="C110" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>9445684</v>
+      </c>
+      <c r="H110" t="n">
+        <v>80</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J110" t="n">
+        <v>21157.81</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B111" t="n">
+        <v>12</v>
+      </c>
+      <c r="C111" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>9445703</v>
+      </c>
+      <c r="H111" t="n">
+        <v>80</v>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J111" t="n">
+        <v>92864.50999999999</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B112" t="n">
+        <v>12</v>
+      </c>
+      <c r="C112" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>9445716</v>
+      </c>
+      <c r="H112" t="n">
+        <v>80</v>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J112" t="n">
+        <v>6498591.83</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B113" t="n">
+        <v>12</v>
+      </c>
+      <c r="C113" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>9445718</v>
+      </c>
+      <c r="H113" t="n">
+        <v>80</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J113" t="n">
+        <v>2401893.13</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B114" t="n">
+        <v>12</v>
+      </c>
+      <c r="C114" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>9445719</v>
+      </c>
+      <c r="H114" t="n">
+        <v>80</v>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J114" t="n">
+        <v>2769856.43</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B115" t="n">
+        <v>12</v>
+      </c>
+      <c r="C115" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>9445721</v>
+      </c>
+      <c r="H115" t="n">
+        <v>80</v>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J115" t="n">
+        <v>3347816.7</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B116" t="n">
+        <v>12</v>
+      </c>
+      <c r="C116" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>9445763</v>
+      </c>
+      <c r="H116" t="n">
+        <v>80</v>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J116" t="n">
+        <v>4576422.1</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B117" t="n">
+        <v>12</v>
+      </c>
+      <c r="C117" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>9447774</v>
+      </c>
+      <c r="H117" t="n">
+        <v>80</v>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J117" t="n">
+        <v>1537.53</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
         <v>2026</v>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Março</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>9999</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>EMG - ADMINISTRACAO DIRETA</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>1321.01.0.1.01.000</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>80</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>17183256.57</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Soma:</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
+      <c r="B118" t="n">
+        <v>1</v>
+      </c>
+      <c r="C118" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>9445683</v>
+      </c>
+      <c r="H118" t="n">
+        <v>80</v>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J118" t="n">
+        <v>1800749.98</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B119" t="n">
+        <v>1</v>
+      </c>
+      <c r="C119" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>9445684</v>
+      </c>
+      <c r="H119" t="n">
+        <v>80</v>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J119" t="n">
+        <v>20434.43</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B120" t="n">
+        <v>1</v>
+      </c>
+      <c r="C120" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>9445703</v>
+      </c>
+      <c r="H120" t="n">
+        <v>80</v>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J120" t="n">
+        <v>89689.62</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B121" t="n">
+        <v>1</v>
+      </c>
+      <c r="C121" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>9445716</v>
+      </c>
+      <c r="H121" t="n">
+        <v>80</v>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J121" t="n">
+        <v>5838234.55</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B122" t="n">
+        <v>1</v>
+      </c>
+      <c r="C122" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>9445718</v>
+      </c>
+      <c r="H122" t="n">
+        <v>80</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J122" t="n">
+        <v>2299629.83</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B123" t="n">
+        <v>1</v>
+      </c>
+      <c r="C123" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>9445719</v>
+      </c>
+      <c r="H123" t="n">
+        <v>80</v>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J123" t="n">
+        <v>2673961.2</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B124" t="n">
+        <v>1</v>
+      </c>
+      <c r="C124" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
+        <v>9445721</v>
+      </c>
+      <c r="H124" t="n">
+        <v>80</v>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J124" t="n">
+        <v>3233361</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B125" t="n">
+        <v>1</v>
+      </c>
+      <c r="C125" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>9445763</v>
+      </c>
+      <c r="H125" t="n">
+        <v>80</v>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J125" t="n">
+        <v>4419962.67</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B126" t="n">
+        <v>1</v>
+      </c>
+      <c r="C126" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>9447774</v>
+      </c>
+      <c r="H126" t="n">
+        <v>80</v>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J126" t="n">
+        <v>1484.98</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B127" t="n">
+        <v>2</v>
+      </c>
+      <c r="C127" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>9445683</v>
+      </c>
+      <c r="H127" t="n">
+        <v>80</v>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J127" t="n">
+        <v>1559881.2</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B128" t="n">
+        <v>2</v>
+      </c>
+      <c r="C128" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>9445684</v>
+      </c>
+      <c r="H128" t="n">
+        <v>80</v>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J128" t="n">
+        <v>17701.13</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B129" t="n">
+        <v>2</v>
+      </c>
+      <c r="C129" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>9445703</v>
+      </c>
+      <c r="H129" t="n">
+        <v>80</v>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J129" t="n">
+        <v>77692.73</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B130" t="n">
+        <v>2</v>
+      </c>
+      <c r="C130" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
+        <v>9445716</v>
+      </c>
+      <c r="H130" t="n">
+        <v>80</v>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J130" t="n">
+        <v>4613147.01</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B131" t="n">
+        <v>2</v>
+      </c>
+      <c r="C131" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>9445718</v>
+      </c>
+      <c r="H131" t="n">
+        <v>80</v>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J131" t="n">
+        <v>1969020.45</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B132" t="n">
+        <v>2</v>
+      </c>
+      <c r="C132" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
+        <v>9445719</v>
+      </c>
+      <c r="H132" t="n">
+        <v>80</v>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J132" t="n">
+        <v>2314914.63</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B133" t="n">
+        <v>2</v>
+      </c>
+      <c r="C133" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>9445721</v>
+      </c>
+      <c r="H133" t="n">
+        <v>80</v>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J133" t="n">
+        <v>2800865.79</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B134" t="n">
+        <v>2</v>
+      </c>
+      <c r="C134" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G134" t="n">
+        <v>9445763</v>
+      </c>
+      <c r="H134" t="n">
+        <v>80</v>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J134" t="n">
+        <v>3828747.29</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B135" t="n">
+        <v>2</v>
+      </c>
+      <c r="C135" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
+        <v>9447774</v>
+      </c>
+      <c r="H135" t="n">
+        <v>80</v>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J135" t="n">
+        <v>1286.34</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B136" t="n">
+        <v>3</v>
+      </c>
+      <c r="C136" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G136" t="n">
+        <v>9445683</v>
+      </c>
+      <c r="H136" t="n">
+        <v>80</v>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J136" t="n">
+        <v>1916211.35</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B137" t="n">
+        <v>3</v>
+      </c>
+      <c r="C137" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G137" t="n">
+        <v>9445684</v>
+      </c>
+      <c r="H137" t="n">
+        <v>80</v>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J137" t="n">
+        <v>21744.68</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B138" t="n">
+        <v>3</v>
+      </c>
+      <c r="C138" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G138" t="n">
+        <v>9445703</v>
+      </c>
+      <c r="H138" t="n">
+        <v>80</v>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J138" t="n">
+        <v>95440.41</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B139" t="n">
+        <v>3</v>
+      </c>
+      <c r="C139" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G139" t="n">
+        <v>9445716</v>
+      </c>
+      <c r="H139" t="n">
+        <v>80</v>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J139" t="n">
+        <v>5487146.31</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B140" t="n">
+        <v>3</v>
+      </c>
+      <c r="C140" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G140" t="n">
+        <v>9445718</v>
+      </c>
+      <c r="H140" t="n">
+        <v>80</v>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J140" t="n">
+        <v>2418812</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B141" t="n">
+        <v>3</v>
+      </c>
+      <c r="C141" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G141" t="n">
+        <v>9445719</v>
+      </c>
+      <c r="H141" t="n">
+        <v>80</v>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J141" t="n">
+        <v>2834875.77</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B142" t="n">
+        <v>3</v>
+      </c>
+      <c r="C142" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G142" t="n">
+        <v>9445721</v>
+      </c>
+      <c r="H142" t="n">
+        <v>80</v>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J142" t="n">
+        <v>3431645.28</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B143" t="n">
+        <v>3</v>
+      </c>
+      <c r="C143" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G143" t="n">
+        <v>9445763</v>
+      </c>
+      <c r="H143" t="n">
+        <v>80</v>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J143" t="n">
+        <v>4703363.96</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B144" t="n">
+        <v>3</v>
+      </c>
+      <c r="C144" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G144" t="n">
+        <v>9447774</v>
+      </c>
+      <c r="H144" t="n">
+        <v>80</v>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J144" t="n">
+        <v>1580.2</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B145" t="n">
+        <v>4</v>
+      </c>
+      <c r="C145" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G145" t="n">
+        <v>9445683</v>
+      </c>
+      <c r="H145" t="n">
+        <v>80</v>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J145" t="n">
+        <v>1743872.77</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B146" t="n">
+        <v>4</v>
+      </c>
+      <c r="C146" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G146" t="n">
+        <v>9445684</v>
+      </c>
+      <c r="H146" t="n">
+        <v>80</v>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J146" t="n">
+        <v>19789.03</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B147" t="n">
+        <v>4</v>
+      </c>
+      <c r="C147" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G147" t="n">
+        <v>9445703</v>
+      </c>
+      <c r="H147" t="n">
+        <v>80</v>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J147" t="n">
+        <v>86856.78</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B148" t="n">
+        <v>4</v>
+      </c>
+      <c r="C148" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G148" t="n">
+        <v>9445716</v>
+      </c>
+      <c r="H148" t="n">
+        <v>80</v>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J148" t="n">
+        <v>4922898.46</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B149" t="n">
+        <v>4</v>
+      </c>
+      <c r="C149" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G149" t="n">
+        <v>9445718</v>
+      </c>
+      <c r="H149" t="n">
+        <v>80</v>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J149" t="n">
+        <v>2200596.37</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B150" t="n">
+        <v>4</v>
+      </c>
+      <c r="C150" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G150" t="n">
+        <v>9445719</v>
+      </c>
+      <c r="H150" t="n">
+        <v>80</v>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J150" t="n">
+        <v>2573224.88</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B151" t="n">
+        <v>4</v>
+      </c>
+      <c r="C151" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G151" t="n">
+        <v>9445721</v>
+      </c>
+      <c r="H151" t="n">
+        <v>80</v>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J151" t="n">
+        <v>3113079.41</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B152" t="n">
+        <v>4</v>
+      </c>
+      <c r="C152" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G152" t="n">
+        <v>9445763</v>
+      </c>
+      <c r="H152" t="n">
+        <v>80</v>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J152" t="n">
+        <v>4280356.81</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B153" t="n">
+        <v>4</v>
+      </c>
+      <c r="C153" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G153" t="n">
+        <v>9447774</v>
+      </c>
+      <c r="H153" t="n">
+        <v>80</v>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J153" t="n">
+        <v>1438.07</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B154" t="n">
+        <v>5</v>
+      </c>
+      <c r="C154" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G154" t="n">
+        <v>9445683</v>
+      </c>
+      <c r="H154" t="n">
+        <v>80</v>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J154" t="n">
+        <v>2605112.85</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B155" t="n">
+        <v>5</v>
+      </c>
+      <c r="C155" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G155" t="n">
+        <v>9445684</v>
+      </c>
+      <c r="H155" t="n">
+        <v>80</v>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J155" t="n">
+        <v>37835.1</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B156" t="n">
+        <v>5</v>
+      </c>
+      <c r="C156" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G156" t="n">
+        <v>9445703</v>
+      </c>
+      <c r="H156" t="n">
+        <v>80</v>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J156" t="n">
+        <v>371000.51</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B157" t="n">
+        <v>5</v>
+      </c>
+      <c r="C157" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G157" t="n">
+        <v>9445716</v>
+      </c>
+      <c r="H157" t="n">
+        <v>80</v>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J157" t="n">
+        <v>12779014.94</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B158" t="n">
+        <v>5</v>
+      </c>
+      <c r="C158" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G158" t="n">
+        <v>9445718</v>
+      </c>
+      <c r="H158" t="n">
+        <v>80</v>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J158" t="n">
+        <v>2188527.46</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B159" t="n">
+        <v>5</v>
+      </c>
+      <c r="C159" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G159" t="n">
+        <v>9445719</v>
+      </c>
+      <c r="H159" t="n">
+        <v>80</v>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J159" t="n">
+        <v>2544564.88</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B160" t="n">
+        <v>5</v>
+      </c>
+      <c r="C160" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G160" t="n">
+        <v>9445721</v>
+      </c>
+      <c r="H160" t="n">
+        <v>80</v>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J160" t="n">
+        <v>3095477.13</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B161" t="n">
+        <v>5</v>
+      </c>
+      <c r="C161" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G161" t="n">
+        <v>9445763</v>
+      </c>
+      <c r="H161" t="n">
+        <v>80</v>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J161" t="n">
+        <v>8171467.76</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B162" t="n">
+        <v>5</v>
+      </c>
+      <c r="C162" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G162" t="n">
+        <v>9447774</v>
+      </c>
+      <c r="H162" t="n">
+        <v>80</v>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J162" t="n">
+        <v>1429.94</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B163" t="n">
+        <v>6</v>
+      </c>
+      <c r="C163" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G163" t="n">
+        <v>9445683</v>
+      </c>
+      <c r="H163" t="n">
+        <v>80</v>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J163" t="n">
+        <v>2685719.5</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B164" t="n">
+        <v>6</v>
+      </c>
+      <c r="C164" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G164" t="n">
+        <v>9445684</v>
+      </c>
+      <c r="H164" t="n">
+        <v>80</v>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J164" t="n">
+        <v>39904.19</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B165" t="n">
+        <v>6</v>
+      </c>
+      <c r="C165" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G165" t="n">
+        <v>9445703</v>
+      </c>
+      <c r="H165" t="n">
+        <v>80</v>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J165" t="n">
+        <v>391289.2</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B166" t="n">
+        <v>6</v>
+      </c>
+      <c r="C166" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G166" t="n">
+        <v>9445716</v>
+      </c>
+      <c r="H166" t="n">
+        <v>80</v>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J166" t="n">
+        <v>12778044.31</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B167" t="n">
+        <v>6</v>
+      </c>
+      <c r="C167" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G167" t="n">
+        <v>9445718</v>
+      </c>
+      <c r="H167" t="n">
+        <v>80</v>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J167" t="n">
+        <v>2469538.84</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B168" t="n">
+        <v>6</v>
+      </c>
+      <c r="C168" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G168" t="n">
+        <v>9445719</v>
+      </c>
+      <c r="H168" t="n">
+        <v>80</v>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J168" t="n">
+        <v>3186363.63</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B169" t="n">
+        <v>6</v>
+      </c>
+      <c r="C169" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G169" t="n">
+        <v>9445721</v>
+      </c>
+      <c r="H169" t="n">
+        <v>80</v>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J169" t="n">
+        <v>3264757.55</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B170" t="n">
+        <v>6</v>
+      </c>
+      <c r="C170" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G170" t="n">
+        <v>9445763</v>
+      </c>
+      <c r="H170" t="n">
+        <v>80</v>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J170" t="n">
+        <v>8618335.710000001</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B171" t="n">
+        <v>6</v>
+      </c>
+      <c r="C171" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G171" t="n">
+        <v>9447774</v>
+      </c>
+      <c r="H171" t="n">
+        <v>80</v>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J171" t="n">
+        <v>1508.14</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B172" t="n">
+        <v>7</v>
+      </c>
+      <c r="C172" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G172" t="n">
+        <v>9445683</v>
+      </c>
+      <c r="H172" t="n">
+        <v>80</v>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J172" t="n">
+        <v>2684528.46</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B173" t="n">
+        <v>7</v>
+      </c>
+      <c r="C173" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G173" t="n">
+        <v>9445684</v>
+      </c>
+      <c r="H173" t="n">
+        <v>80</v>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J173" t="n">
+        <v>43755.01</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B174" t="n">
+        <v>7</v>
+      </c>
+      <c r="C174" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G174" t="n">
+        <v>9445703</v>
+      </c>
+      <c r="H174" t="n">
+        <v>80</v>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J174" t="n">
+        <v>429049.41</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B175" t="n">
+        <v>7</v>
+      </c>
+      <c r="C175" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G175" t="n">
+        <v>9445716</v>
+      </c>
+      <c r="H175" t="n">
+        <v>80</v>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J175" t="n">
+        <v>12045147.37</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B176" t="n">
+        <v>7</v>
+      </c>
+      <c r="C176" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G176" t="n">
+        <v>9445718</v>
+      </c>
+      <c r="H176" t="n">
+        <v>80</v>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J176" t="n">
+        <v>3151905.7</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B177" t="n">
+        <v>7</v>
+      </c>
+      <c r="C177" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G177" t="n">
+        <v>9445719</v>
+      </c>
+      <c r="H177" t="n">
+        <v>80</v>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J177" t="n">
+        <v>4887257.73</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B178" t="n">
+        <v>7</v>
+      </c>
+      <c r="C178" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G178" t="n">
+        <v>9445721</v>
+      </c>
+      <c r="H178" t="n">
+        <v>80</v>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J178" t="n">
+        <v>3579813.42</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B179" t="n">
+        <v>7</v>
+      </c>
+      <c r="C179" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G179" t="n">
+        <v>9445763</v>
+      </c>
+      <c r="H179" t="n">
+        <v>80</v>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J179" t="n">
+        <v>9450022.970000001</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B180" t="n">
+        <v>7</v>
+      </c>
+      <c r="C180" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G180" t="n">
+        <v>9447774</v>
+      </c>
+      <c r="H180" t="n">
+        <v>80</v>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="J180" t="n">
+        <v>1653.68</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr"/>
+      <c r="B181" t="inlineStr"/>
+      <c r="C181" t="inlineStr"/>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="n">
         <v>367329713</v>
       </c>
     </row>
